--- a/docs/materiale-de-mapat.xlsx
+++ b/docs/materiale-de-mapat.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="184">
   <si>
     <t>Model</t>
   </si>
@@ -52,102 +52,90 @@
     <t>TABURETE</t>
   </si>
   <si>
-    <t>VATELINA</t>
+    <t>CAPSE 38/12</t>
+  </si>
+  <si>
+    <t>SUTEB</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>00009232  CAPSE 80/12 (CUT)</t>
+  </si>
+  <si>
+    <t>00006350  CAPSE 380/12 E-NEW (MIIB)</t>
+  </si>
+  <si>
+    <t>00002287  CAPSE (BUC)</t>
+  </si>
+  <si>
+    <t>PICIOARE</t>
+  </si>
+  <si>
+    <t>MIIB</t>
+  </si>
+  <si>
+    <t>00016608  PICIOARE MOBILA (BUC)</t>
+  </si>
+  <si>
+    <t>00004482  PICIOARE CONICE NEGRE (BUC)</t>
+  </si>
+  <si>
+    <t>00012787  PICIOARE KLOBO SET MP (SET)</t>
+  </si>
+  <si>
+    <t>POL2542</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>00010335  POLIURETAN FASII VR 2542 (KG)</t>
+  </si>
+  <si>
+    <t>00001305  POLIURETAN 2542X2000X2000X20 (B)</t>
+  </si>
+  <si>
+    <t>00001985  POLIURETAN 2542X130X40 (BUC)</t>
+  </si>
+  <si>
+    <t>CANAPEA-MARIA</t>
+  </si>
+  <si>
+    <t>CHERESTEA RAS</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>00004311  CHERESTEA (MC)</t>
+  </si>
+  <si>
+    <t>00000033  CHERESTEA RASINOASE (MC)</t>
+  </si>
+  <si>
+    <t>00009371  CHERESTEA FAG TAS (MC)</t>
+  </si>
+  <si>
+    <t>CHER FAG</t>
+  </si>
+  <si>
+    <t>00000034  CHERESTEA FAG (MC)</t>
+  </si>
+  <si>
+    <t>00021033  CHERESTELE FAG (MC)</t>
+  </si>
+  <si>
+    <t>00006836  CHIT FAG (KG)</t>
+  </si>
+  <si>
+    <t>HDF MELAM 2.5 MM ALB</t>
   </si>
   <si>
     <t>MP</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>00007949  VASELINA (BUC)</t>
-  </si>
-  <si>
-    <t>00000270  VATELINA 100GR (ML)</t>
-  </si>
-  <si>
-    <t>00003822  VATELINA 300GR (MP)</t>
-  </si>
-  <si>
-    <t>CAPSE 38/12</t>
-  </si>
-  <si>
-    <t>SUTEB</t>
-  </si>
-  <si>
-    <t>00009232  CAPSE 80/12 (CUT)</t>
-  </si>
-  <si>
-    <t>00006350  CAPSE 380/12 E-NEW (MIIB)</t>
-  </si>
-  <si>
-    <t>00002287  CAPSE (BUC)</t>
-  </si>
-  <si>
-    <t>PICIOARE</t>
-  </si>
-  <si>
-    <t>MIIB</t>
-  </si>
-  <si>
-    <t>00016608  PICIOARE MOBILA (BUC)</t>
-  </si>
-  <si>
-    <t>00004482  PICIOARE CONICE NEGRE (BUC)</t>
-  </si>
-  <si>
-    <t>00012787  PICIOARE KLOBO SET MP (SET)</t>
-  </si>
-  <si>
-    <t>POL2542</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>00010335  POLIURETAN FASII VR 2542 (KG)</t>
-  </si>
-  <si>
-    <t>00001305  POLIURETAN 2542X2000X2000X20 (B)</t>
-  </si>
-  <si>
-    <t>00001985  POLIURETAN 2542X130X40 (BUC)</t>
-  </si>
-  <si>
-    <t>CANAPEA-MARIA</t>
-  </si>
-  <si>
-    <t>CHERESTEA RAS</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
-    <t>00004311  CHERESTEA (MC)</t>
-  </si>
-  <si>
-    <t>00000033  CHERESTEA RASINOASE (MC)</t>
-  </si>
-  <si>
-    <t>00009371  CHERESTEA FAG TAS (MC)</t>
-  </si>
-  <si>
-    <t>CHER FAG</t>
-  </si>
-  <si>
-    <t>00000034  CHERESTEA FAG (MC)</t>
-  </si>
-  <si>
-    <t>00021033  CHERESTELE FAG (MC)</t>
-  </si>
-  <si>
-    <t>00006836  CHIT FAG (KG)</t>
-  </si>
-  <si>
-    <t>HDF MELAM 2.5 MM ALB</t>
-  </si>
-  <si>
     <t>00013002  MDF MELAM.,2 FETE,10MM ALB (MP)</t>
   </si>
   <si>
@@ -307,27 +295,12 @@
     <t>00007506  BANDA ATC (BUC)</t>
   </si>
   <si>
-    <t>00006427  BANDA ETANS (M)</t>
+    <t>00001147  SCOTCH MARE (BUC)</t>
   </si>
   <si>
     <t>CANAPEA-CORINA</t>
   </si>
   <si>
-    <t>PVC</t>
-  </si>
-  <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>00005876  PAT PVC (BUC)</t>
-  </si>
-  <si>
-    <t>00006583  TUB PVC (BUC)</t>
-  </si>
-  <si>
-    <t>00010725  COT PVC (BUC)</t>
-  </si>
-  <si>
     <t>HSURUB STAS 5/40</t>
   </si>
   <si>
@@ -355,7 +328,7 @@
     <t>00010978  SAIBE PLATE DIN 125A-M12X24X2.5 ZA (BUC)</t>
   </si>
   <si>
-    <t>00006696  SAIBA PLATA SPECIALA M8X24X2 ZA (MIIB)</t>
+    <t>00002732  SAIBE PLATE DIN 125 M10 (BUC)</t>
   </si>
   <si>
     <t>HSURUB 5/20</t>
@@ -394,15 +367,15 @@
     <t>CURSORI</t>
   </si>
   <si>
+    <t>00000965  CURSORI ALBI (BUC)</t>
+  </si>
+  <si>
     <t>00003621  CURSOR 3 (BC)</t>
   </si>
   <si>
     <t>00010744  CURSOR 5 (BUC)</t>
   </si>
   <si>
-    <t>00015903  CURSOR RT3 BEJ308 (BUC)</t>
-  </si>
-  <si>
     <t>OPRITORI PLASTIC</t>
   </si>
   <si>
@@ -412,7 +385,7 @@
     <t>00001819  MATURI PLASTIC (BUC)</t>
   </si>
   <si>
-    <t>00001408  DOSAR PLASTIC (B)</t>
+    <t>00001117  PUNGI PLASTIC (BUC)</t>
   </si>
   <si>
     <t>CANAPEA-CORINA-II</t>
@@ -448,12 +421,12 @@
     <t>00011925  PLASA BONNEL 122*61*9.5 (BUC)</t>
   </si>
   <si>
+    <t>00000320  PLASA BONNELL 9.5 (BUC)</t>
+  </si>
+  <si>
     <t>00000385  PLASA BONEL 186X66X9.5 ()</t>
   </si>
   <si>
-    <t>00011653  PLASA BONNELL 122*61*9.5CM S2.4MM (BUC)</t>
-  </si>
-  <si>
     <t>SAIBE PLATE M8.4x24x1.5</t>
   </si>
   <si>
@@ -469,7 +442,7 @@
     <t>00003770  ROTILA CU FLANSA 40MM (BUC)</t>
   </si>
   <si>
-    <t>00012892  ROTILA SFERICA CAUCIUC D40 CU FLANSA (BUC)</t>
+    <t>00003771  ROTILA CU FLANSA SI FRANA (BUC)</t>
   </si>
   <si>
     <t>ROTILA 30 MM SW12 NEGRU</t>
@@ -526,6 +499,9 @@
     <t>00003806  HOLZSURUB (BUC)</t>
   </si>
   <si>
+    <t>00005630  HOLTZSURUB 5.0X7.0 (100B)</t>
+  </si>
+  <si>
     <t>00012774  HOLTZSURUB CAP INECAT 3.5X40 (BUC)</t>
   </si>
   <si>
@@ -538,9 +514,6 @@
     <t>HOLZSURUB 5X20</t>
   </si>
   <si>
-    <t>00000393  HOLSURUB (BUC)</t>
-  </si>
-  <si>
     <t>HOLZSURUB 5X60</t>
   </si>
   <si>
@@ -563,18 +536,6 @@
   </si>
   <si>
     <t>00003875  SURUB TORBANT M8X80 (MIIB)</t>
-  </si>
-  <si>
-    <t>PIULITE M6</t>
-  </si>
-  <si>
-    <t>00021088  PIULITE M10 (BUC)</t>
-  </si>
-  <si>
-    <t>00001233  PIULITA (B)</t>
-  </si>
-  <si>
-    <t>00025000  PIULITA (BUC)</t>
   </si>
   <si>
     <t>PICIOR MD PL NEGRU</t>
@@ -991,7 +952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1051,7 +1012,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -1060,7 +1021,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="2">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>15</v>
@@ -1069,19 +1030,19 @@
         <v>16</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
       </c>
       <c r="J2">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
       </c>
       <c r="L2">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1089,7 +1050,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -1098,7 +1059,7 @@
         <v>20</v>
       </c>
       <c r="E3" s="2">
-        <v>0.3</v>
+        <v>0.004</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>15</v>
@@ -1107,19 +1068,19 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
       <c r="J3">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K3" t="s">
         <v>23</v>
       </c>
       <c r="L3">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1127,7 +1088,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
@@ -1136,7 +1097,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="2">
-        <v>0.004</v>
+        <v>0.24</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>15</v>
@@ -1145,112 +1106,112 @@
         <v>26</v>
       </c>
       <c r="H4">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s">
         <v>27</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
         <v>28</v>
       </c>
       <c r="L4">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2">
-        <v>0.24</v>
+        <v>0.0255</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J5">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
       </c>
       <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.0234</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="2">
-        <v>0.0255</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6">
+        <v>64</v>
+      </c>
+      <c r="I6" t="s">
         <v>37</v>
       </c>
-      <c r="H6">
-        <v>77</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="J6">
+        <v>62</v>
+      </c>
+      <c r="K6" t="s">
         <v>38</v>
       </c>
-      <c r="J6">
-        <v>72</v>
-      </c>
-      <c r="K6" t="s">
-        <v>39</v>
-      </c>
       <c r="L6">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
       <c r="E7" s="2">
-        <v>0.0234</v>
+        <v>1.133</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>15</v>
@@ -1259,36 +1220,36 @@
         <v>41</v>
       </c>
       <c r="H7">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
       </c>
       <c r="L7">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2">
-        <v>1.133</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>15</v>
@@ -1297,27 +1258,27 @@
         <v>45</v>
       </c>
       <c r="H8">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
         <v>46</v>
       </c>
       <c r="J8">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
         <v>47</v>
       </c>
       <c r="L8">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -1326,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="2">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>15</v>
@@ -1335,33 +1296,33 @@
         <v>49</v>
       </c>
       <c r="H9">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I9" t="s">
         <v>50</v>
       </c>
       <c r="J9">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
         <v>51</v>
       </c>
       <c r="L9">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2">
         <v>0.08</v>
@@ -1385,62 +1346,62 @@
         <v>55</v>
       </c>
       <c r="L10">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
         <v>57</v>
       </c>
-      <c r="H11">
-        <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>58</v>
-      </c>
       <c r="J11">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L11">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>15</v>
@@ -1449,16 +1410,16 @@
         <v>57</v>
       </c>
       <c r="H12">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J12">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L12">
         <v>48</v>
@@ -1466,57 +1427,57 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
       <c r="E13" s="2">
-        <v>0.14</v>
+        <v>0.004</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H13">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J13">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L13">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2">
-        <v>0.004</v>
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>15</v>
@@ -1525,36 +1486,36 @@
         <v>67</v>
       </c>
       <c r="H14">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I14" t="s">
         <v>68</v>
       </c>
       <c r="J14">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="K14" t="s">
         <v>69</v>
       </c>
       <c r="L14">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
         <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>15</v>
@@ -1563,74 +1524,74 @@
         <v>71</v>
       </c>
       <c r="H15">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I15" t="s">
         <v>72</v>
       </c>
       <c r="J15">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K15" t="s">
         <v>73</v>
       </c>
       <c r="L15">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
         <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J16">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="K16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L16">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>15</v>
@@ -1639,36 +1600,36 @@
         <v>80</v>
       </c>
       <c r="H17">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s">
         <v>81</v>
       </c>
       <c r="J17">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="K17" t="s">
         <v>82</v>
       </c>
       <c r="L17">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>0.13</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>15</v>
@@ -1683,30 +1644,30 @@
         <v>85</v>
       </c>
       <c r="J18">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K18" t="s">
         <v>86</v>
       </c>
       <c r="L18">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
         <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="E19" s="2">
-        <v>0.13</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>15</v>
@@ -1715,36 +1676,36 @@
         <v>88</v>
       </c>
       <c r="H19">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="I19" t="s">
         <v>89</v>
       </c>
       <c r="J19">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="K19" t="s">
         <v>90</v>
       </c>
       <c r="L19">
-        <v>74</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
         <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>15</v>
@@ -1753,206 +1714,206 @@
         <v>92</v>
       </c>
       <c r="H20">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="I20" t="s">
         <v>93</v>
       </c>
       <c r="J20">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K20" t="s">
         <v>94</v>
       </c>
       <c r="L20">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.0237</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21">
+        <v>77</v>
+      </c>
+      <c r="I21" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21">
+        <v>72</v>
+      </c>
+      <c r="K21" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="1">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H21">
-        <v>57</v>
-      </c>
-      <c r="I21" t="s">
-        <v>97</v>
-      </c>
-      <c r="J21">
-        <v>48</v>
-      </c>
-      <c r="K21" t="s">
-        <v>98</v>
-      </c>
       <c r="L21">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B22" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="H22">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="J22">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K22" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="L22">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B23" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2">
-        <v>0.0237</v>
+        <v>1.33</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H23">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J23">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L23">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B24" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
         <v>40</v>
       </c>
-      <c r="D24" t="s">
-        <v>36</v>
-      </c>
       <c r="E24" s="2">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H24">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J24">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L24">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B25" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="2">
-        <v>1.33</v>
+        <v>0.08</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H25">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I25" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J25">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L25">
         <v>55</v>
@@ -1960,151 +1921,151 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B26" s="1">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="2">
-        <v>1.2</v>
+        <v>0.08</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H26">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="I26" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J26">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="K26" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="L26">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="1">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="1">
-        <v>20</v>
-      </c>
-      <c r="C27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" t="s">
-        <v>53</v>
-      </c>
       <c r="H27">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I27" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>57</v>
       </c>
       <c r="K27" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="L27">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28">
+        <v>70</v>
+      </c>
+      <c r="I28" t="s">
+        <v>104</v>
+      </c>
+      <c r="J28">
+        <v>56</v>
+      </c>
+      <c r="K28" t="s">
         <v>105</v>
       </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28">
+      <c r="L28">
         <v>52</v>
-      </c>
-      <c r="I28" t="s">
-        <v>58</v>
-      </c>
-      <c r="J28">
-        <v>48</v>
-      </c>
-      <c r="K28" t="s">
-        <v>106</v>
-      </c>
-      <c r="L28">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B29" s="1">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s">
         <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" t="s">
-        <v>108</v>
       </c>
       <c r="H29">
         <v>67</v>
       </c>
       <c r="I29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J29">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K29" t="s">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="L29">
         <v>56</v>
@@ -2112,282 +2073,282 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B30" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="H30">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I30" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="J30">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K30" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="L30">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B31" s="1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E31" s="2">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H31">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J31">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="K31" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="L31">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B32" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E32" s="2">
-        <v>0.14</v>
+        <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="H32">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I32" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="J32">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K32" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="L32">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B33" s="1">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2">
-        <v>2</v>
+        <v>0.004</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="H33">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I33" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="J33">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K33" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="L33">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B34" s="1">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H34">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I34" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J34">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K34" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="L34">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B35" s="1">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E35" s="2">
-        <v>0.004</v>
+        <v>2</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="H35">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I35" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="J35">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K35" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="L35">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B36" s="1">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E36" s="2">
-        <v>3</v>
+        <v>0.13</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="H36">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="I36" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="J36">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="L36">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B37" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="E37" s="2">
         <v>2</v>
@@ -2396,323 +2357,323 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="H37">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="I37" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="J37">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="K37" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="L37">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B38" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H38">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="I38" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J38">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="K38" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L38">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B39" s="1">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E39" s="2">
-        <v>2</v>
+        <v>0.027</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="H39">
+        <v>77</v>
+      </c>
+      <c r="I39" t="s">
         <v>33</v>
       </c>
-      <c r="I39" t="s">
-        <v>93</v>
-      </c>
       <c r="J39">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="K39" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="L39">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B40" s="1">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E40" s="2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="H40">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="J40">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="K40" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="L40">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B41" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="E41" s="2">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="H41">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I41" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="J41">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K41" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="L41">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B42" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E42" s="2">
-        <v>0.027</v>
+        <v>0.654</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H42">
         <v>77</v>
       </c>
       <c r="I42" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J42">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K42" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L42">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B43" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43" t="s">
         <v>40</v>
       </c>
-      <c r="D43" t="s">
-        <v>36</v>
-      </c>
       <c r="E43" s="2">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="H43">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="J43">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K43" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="L43">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B44" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E44" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="H44">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="I44" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="J44">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K44" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="L44">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>125</v>
+      </c>
+      <c r="B45" s="1">
+        <v>17</v>
+      </c>
+      <c r="C45" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="1">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s">
-        <v>48</v>
-      </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E45" s="2">
-        <v>0.654</v>
+        <v>2</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="H45">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I45" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="J45">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K45" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="L45">
         <v>65</v>
@@ -2720,931 +2681,931 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B46" s="1">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="2">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="H46">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I46" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="J46">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K46" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="L46">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B47" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="E47" s="2">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="H47">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I47" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="J47">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K47" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="L47">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B48" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="E48" s="2">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="H48">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I48" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="J48">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K48" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="L48">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B49" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>139</v>
+      </c>
+      <c r="H49">
+        <v>59</v>
+      </c>
+      <c r="I49" t="s">
+        <v>103</v>
+      </c>
+      <c r="J49">
+        <v>59</v>
+      </c>
+      <c r="K49" t="s">
+        <v>104</v>
+      </c>
+      <c r="L49">
         <v>52</v>
-      </c>
-      <c r="D49" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" t="s">
-        <v>53</v>
-      </c>
-      <c r="H49">
-        <v>60</v>
-      </c>
-      <c r="I49" t="s">
-        <v>54</v>
-      </c>
-      <c r="J49">
-        <v>57</v>
-      </c>
-      <c r="K49" t="s">
-        <v>55</v>
-      </c>
-      <c r="L49">
-        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B50" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>107</v>
+      </c>
+      <c r="H50">
+        <v>67</v>
+      </c>
+      <c r="I50" t="s">
+        <v>108</v>
+      </c>
+      <c r="J50">
         <v>56</v>
       </c>
-      <c r="D50" t="s">
-        <v>20</v>
-      </c>
-      <c r="E50" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G50" t="s">
-        <v>57</v>
-      </c>
-      <c r="H50">
-        <v>60</v>
-      </c>
-      <c r="I50" t="s">
-        <v>58</v>
-      </c>
-      <c r="J50">
-        <v>57</v>
-      </c>
       <c r="K50" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L50">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B51" s="1">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E51" s="2">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="H51">
         <v>67</v>
       </c>
       <c r="I51" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="J51">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K51" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="L51">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B52" s="1">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E52" s="2">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H52">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="J52">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K52" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="L52">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B53" s="1">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E53" s="2">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="H53">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="J53">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K53" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="L53">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B54" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="D54" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="2">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="H54">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="I54" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
       <c r="J54">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="L54">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E55" s="2">
-        <v>2</v>
+        <v>0.004</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="H55">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="I55" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="J55">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="K55" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="L55">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B56" s="1">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C56" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" t="s">
+        <v>40</v>
+      </c>
+      <c r="E56" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56">
+        <v>70</v>
+      </c>
+      <c r="I56" t="s">
         <v>153</v>
       </c>
-      <c r="D56" t="s">
-        <v>79</v>
-      </c>
-      <c r="E56" s="2">
-        <v>2</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" t="s">
-        <v>154</v>
-      </c>
-      <c r="H56">
-        <v>88</v>
-      </c>
-      <c r="I56" t="s">
-        <v>155</v>
-      </c>
       <c r="J56">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K56" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="L56">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B57" s="1">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C57" t="s">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="D57" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="H57">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I57" t="s">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="J57">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="K57" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="L57">
-        <v>79</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B58" s="1">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C58" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D58" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="E58" s="2">
-        <v>0.004</v>
+        <v>2</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="H58">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="I58" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="J58">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="K58" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="L58">
-        <v>65</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B59" s="1">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C59" t="s">
-        <v>160</v>
+        <v>91</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E59" s="2">
-        <v>4.5</v>
+        <v>0.3</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="H59">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="I59" t="s">
-        <v>162</v>
+        <v>93</v>
       </c>
       <c r="J59">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="K59" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="L59">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="B60" s="1">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E60" s="2">
-        <v>2</v>
+        <v>0.0292</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="H60">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I60" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="J60">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="K60" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="L60">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="B61" s="1">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E61" s="2">
-        <v>2</v>
+        <v>0.0347</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="H61">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="I61" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="J61">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="K61" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="L61">
-        <v>29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="B62" s="1">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="E62" s="2">
-        <v>0.3</v>
+        <v>2.44</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="H62">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I62" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="J62">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K62" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="L62">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B63" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E63" s="2">
-        <v>0.4</v>
+        <v>2.23</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="H63">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="J63">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="K63" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="L63">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B64" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2">
-        <v>0.0292</v>
+        <v>1</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="H64">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="I64" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="J64">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="K64" t="s">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="L64">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B65" s="1">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="D65" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="E65" s="2">
-        <v>0.0347</v>
+        <v>2</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="H65">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="I65" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="J65">
+        <v>73</v>
+      </c>
+      <c r="K65" t="s">
+        <v>112</v>
+      </c>
+      <c r="L65">
         <v>62</v>
-      </c>
-      <c r="K65" t="s">
-        <v>43</v>
-      </c>
-      <c r="L65">
-        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B66" s="1">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E66" s="2">
-        <v>2.44</v>
+        <v>10</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="H66">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I66" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="J66">
+        <v>65</v>
+      </c>
+      <c r="K66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L66">
         <v>56</v>
-      </c>
-      <c r="K66" t="s">
-        <v>47</v>
-      </c>
-      <c r="L66">
-        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B67" s="1">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="E67" s="2">
-        <v>2.23</v>
+        <v>6</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="H67">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I67" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="J67">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K67" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="L67">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B68" s="1">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>164</v>
+        <v>58</v>
       </c>
       <c r="D68" t="s">
-        <v>165</v>
+        <v>14</v>
       </c>
       <c r="E68" s="2">
-        <v>1</v>
+        <v>0.14</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>166</v>
+        <v>57</v>
       </c>
       <c r="H68">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I68" t="s">
-        <v>167</v>
+        <v>59</v>
       </c>
       <c r="J68">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="K68" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="L68">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>154</v>
+      </c>
+      <c r="B69" s="1">
+        <v>30</v>
+      </c>
+      <c r="C69" t="s">
+        <v>160</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69">
+        <v>74</v>
+      </c>
+      <c r="I69" t="s">
+        <v>162</v>
+      </c>
+      <c r="J69">
+        <v>63</v>
+      </c>
+      <c r="K69" t="s">
         <v>163</v>
       </c>
-      <c r="B69" s="1">
-        <v>23</v>
-      </c>
-      <c r="C69" t="s">
-        <v>118</v>
-      </c>
-      <c r="D69" t="s">
-        <v>79</v>
-      </c>
-      <c r="E69" s="2">
-        <v>2</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" t="s">
-        <v>119</v>
-      </c>
-      <c r="H69">
-        <v>73</v>
-      </c>
-      <c r="I69" t="s">
-        <v>120</v>
-      </c>
-      <c r="J69">
-        <v>73</v>
-      </c>
-      <c r="K69" t="s">
-        <v>121</v>
-      </c>
       <c r="L69">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B70" s="1">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D70" t="s">
         <v>14</v>
       </c>
       <c r="E70" s="2">
-        <v>10</v>
+        <v>0.14</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>15</v>
@@ -3653,112 +3614,112 @@
         <v>161</v>
       </c>
       <c r="H70">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I70" t="s">
         <v>162</v>
       </c>
       <c r="J70">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K70" t="s">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="L70">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B71" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="D71" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="E71" s="2">
-        <v>6</v>
+        <v>0.04</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="H71">
+        <v>74</v>
+      </c>
+      <c r="I71" t="s">
+        <v>107</v>
+      </c>
+      <c r="J71">
+        <v>73</v>
+      </c>
+      <c r="K71" t="s">
+        <v>162</v>
+      </c>
+      <c r="L71">
         <v>63</v>
-      </c>
-      <c r="I71" t="s">
-        <v>128</v>
-      </c>
-      <c r="J71">
-        <v>63</v>
-      </c>
-      <c r="K71" t="s">
-        <v>129</v>
-      </c>
-      <c r="L71">
-        <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B72" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C72" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="D72" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E72" s="2">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="H72">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I72" t="s">
+        <v>162</v>
+      </c>
+      <c r="J72">
         <v>63</v>
       </c>
-      <c r="J72">
-        <v>60</v>
-      </c>
       <c r="K72" t="s">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="L72">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B73" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C73" t="s">
         <v>169</v>
       </c>
       <c r="D73" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E73" s="2">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>15</v>
@@ -3767,130 +3728,130 @@
         <v>170</v>
       </c>
       <c r="H73">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I73" t="s">
         <v>171</v>
       </c>
       <c r="J73">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="K73" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="L73">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B74" s="1">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D74" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E74" s="2">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G74" t="s">
+        <v>174</v>
+      </c>
+      <c r="H74">
+        <v>83</v>
+      </c>
+      <c r="I74" t="s">
         <v>170</v>
       </c>
-      <c r="H74">
-        <v>74</v>
-      </c>
-      <c r="I74" t="s">
-        <v>173</v>
-      </c>
       <c r="J74">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="K74" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="L74">
-        <v>55</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B75" s="1">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="D75" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E75" s="2">
-        <v>0.04</v>
+        <v>4</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="H75">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I75" t="s">
+        <v>115</v>
+      </c>
+      <c r="J75">
+        <v>58</v>
+      </c>
+      <c r="K75" t="s">
         <v>116</v>
       </c>
-      <c r="J75">
-        <v>73</v>
-      </c>
-      <c r="K75" t="s">
-        <v>175</v>
-      </c>
       <c r="L75">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B76" s="1">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="D76" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E76" s="2">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="H76">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="I76" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="J76">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K76" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="L76">
         <v>55</v>
@@ -3898,419 +3859,229 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B77" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
         <v>20</v>
       </c>
       <c r="E77" s="2">
-        <v>0.04</v>
+        <v>2</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>179</v>
+        <v>16</v>
       </c>
       <c r="H77">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I77" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="J77">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K77" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="L77">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B78" s="1">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C78" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D78" t="s">
         <v>20</v>
       </c>
       <c r="E78" s="2">
-        <v>0.04</v>
+        <v>0.013</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H78">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I78" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J78">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K78" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L78">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B79" s="1">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>184</v>
+        <v>83</v>
       </c>
       <c r="D79" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="E79" s="2">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="H79">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="I79" t="s">
-        <v>186</v>
+        <v>85</v>
       </c>
       <c r="J79">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="K79" t="s">
-        <v>187</v>
+        <v>86</v>
       </c>
       <c r="L79">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B80" s="1">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="D80" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="E80" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="H80">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I80" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="J80">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K80" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="L80">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B81" s="1">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C81" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="D81" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E81" s="2">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="H81">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="I81" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="J81">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K81" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="L81">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B82" s="1">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="D82" t="s">
         <v>25</v>
       </c>
       <c r="E82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="H82">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="I82" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="J82">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="K82" t="s">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="L82">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>163</v>
-      </c>
-      <c r="B83" s="1">
-        <v>46</v>
-      </c>
-      <c r="C83" t="s">
-        <v>188</v>
-      </c>
-      <c r="D83" t="s">
-        <v>25</v>
-      </c>
-      <c r="E83" s="2">
-        <v>0.013</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" t="s">
-        <v>189</v>
-      </c>
-      <c r="H83">
-        <v>88</v>
-      </c>
-      <c r="I83" t="s">
-        <v>190</v>
-      </c>
-      <c r="J83">
-        <v>77</v>
-      </c>
-      <c r="K83" t="s">
-        <v>191</v>
-      </c>
-      <c r="L83">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>163</v>
-      </c>
-      <c r="B84" s="1">
-        <v>49</v>
-      </c>
-      <c r="C84" t="s">
-        <v>87</v>
-      </c>
-      <c r="D84" t="s">
-        <v>192</v>
-      </c>
-      <c r="E84" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G84" t="s">
-        <v>88</v>
-      </c>
-      <c r="H84">
-        <v>83</v>
-      </c>
-      <c r="I84" t="s">
-        <v>89</v>
-      </c>
-      <c r="J84">
-        <v>74</v>
-      </c>
-      <c r="K84" t="s">
-        <v>90</v>
-      </c>
-      <c r="L84">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>163</v>
-      </c>
-      <c r="B85" s="1">
-        <v>50</v>
-      </c>
-      <c r="C85" t="s">
-        <v>193</v>
-      </c>
-      <c r="D85" t="s">
-        <v>30</v>
-      </c>
-      <c r="E85" s="2">
-        <v>2</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" t="s">
-        <v>194</v>
-      </c>
-      <c r="H85">
-        <v>64</v>
-      </c>
-      <c r="I85" t="s">
-        <v>195</v>
-      </c>
-      <c r="J85">
-        <v>64</v>
-      </c>
-      <c r="K85" t="s">
-        <v>196</v>
-      </c>
-      <c r="L85">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>163</v>
-      </c>
-      <c r="B86" s="1">
-        <v>51</v>
-      </c>
-      <c r="C86" t="s">
-        <v>95</v>
-      </c>
-      <c r="D86" t="s">
-        <v>79</v>
-      </c>
-      <c r="E86" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G86" t="s">
-        <v>96</v>
-      </c>
-      <c r="H86">
-        <v>57</v>
-      </c>
-      <c r="I86" t="s">
-        <v>97</v>
-      </c>
-      <c r="J86">
-        <v>48</v>
-      </c>
-      <c r="K86" t="s">
-        <v>98</v>
-      </c>
-      <c r="L86">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>163</v>
-      </c>
-      <c r="B87" s="1">
-        <v>53</v>
-      </c>
-      <c r="C87" t="s">
-        <v>91</v>
-      </c>
-      <c r="D87" t="s">
-        <v>30</v>
-      </c>
-      <c r="E87" s="2">
-        <v>3</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" t="s">
-        <v>92</v>
-      </c>
-      <c r="H87">
-        <v>33</v>
-      </c>
-      <c r="I87" t="s">
-        <v>93</v>
-      </c>
-      <c r="J87">
-        <v>29</v>
-      </c>
-      <c r="K87" t="s">
-        <v>94</v>
-      </c>
-      <c r="L87">
         <v>29</v>
       </c>
     </row>

--- a/docs/materiale-de-mapat.xlsx
+++ b/docs/materiale-de-mapat.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="219">
   <si>
     <t>Model</t>
   </si>
@@ -37,7 +37,10 @@
     <t>Cât de des</t>
   </si>
   <si>
-    <t>Cantitate/buc</t>
+    <t>Cantitate/buc (recent)</t>
+  </si>
+  <si>
+    <t>S-a schimbat?</t>
   </si>
   <si>
     <t>Din istoricul de producție 2</t>
@@ -67,523 +70,529 @@
     <t>00009232  CAPSE 80/12 (CUT)</t>
   </si>
   <si>
+    <t>23%</t>
+  </si>
+  <si>
+    <t>00006350  CAPSE 380/12 E-NEW (MIIB)</t>
+  </si>
+  <si>
+    <t>00000023  CAPSE 380/14 (BUC)</t>
+  </si>
+  <si>
+    <t>00009232  CAPSE 80/12 (CUT) 69%</t>
+  </si>
+  <si>
+    <t>00006350  CAPSE 380/12 E-NEW (MIIB) 61%</t>
+  </si>
+  <si>
+    <t>PICIOARE</t>
+  </si>
+  <si>
+    <t>MIIB</t>
+  </si>
+  <si>
+    <t>00011469  PICIOR D50 H50 (BUC)</t>
+  </si>
+  <si>
+    <t>8%</t>
+  </si>
+  <si>
+    <t>00016608  PICIOARE MOBILA (BUC) 67%</t>
+  </si>
+  <si>
+    <t>00004482  PICIOARE CONICE NEGRE (BUC) 63%</t>
+  </si>
+  <si>
+    <t>POL2542</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>00010335  POLIURETAN FASII VR 2542 (KG) 40%</t>
+  </si>
+  <si>
+    <t>00001305  POLIURETAN 2542X2000X2000X20 (B) 36%</t>
+  </si>
+  <si>
+    <t>CANAPEA-MARIA</t>
+  </si>
+  <si>
+    <t>CHERESTEA RAS</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>00002310</t>
+  </si>
+  <si>
+    <t>✓ 00002310  CHERESTEA TIVITA RASINOASE (MC)</t>
+  </si>
+  <si>
     <t>40%</t>
   </si>
   <si>
-    <t>00006350  CAPSE 380/12 E-NEW (MIIB)</t>
-  </si>
-  <si>
-    <t>00010483  CAPSE 380/14 - NEW (MII B)</t>
-  </si>
-  <si>
-    <t>00009232  CAPSE 80/12 (CUT) 69%</t>
-  </si>
-  <si>
-    <t>00006350  CAPSE 380/12 E-NEW (MIIB) 61%</t>
-  </si>
-  <si>
-    <t>PICIOARE</t>
-  </si>
-  <si>
-    <t>MIIB</t>
-  </si>
-  <si>
-    <t>00011469  PICIOR D50 H50 (BUC)</t>
+    <t>înainte: 0.0300</t>
+  </si>
+  <si>
+    <t>00024880  CHERESTEA TIVITA FRASIN (MC)</t>
+  </si>
+  <si>
+    <t>00016024  CHERESTEA TIVITA FAG (MC)</t>
+  </si>
+  <si>
+    <t>00004311  CHERESTEA (MC) 77%</t>
+  </si>
+  <si>
+    <t>00000033  CHERESTEA RASINOASE (MC) 72%</t>
+  </si>
+  <si>
+    <t>CHER FAG</t>
+  </si>
+  <si>
+    <t>00016024</t>
+  </si>
+  <si>
+    <t>✓ 00016024  CHERESTEA TIVITA FAG (MC)</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>00000034  CHERESTEA FAG (MC) 64%</t>
+  </si>
+  <si>
+    <t>00021033  CHERESTELE FAG (MC) 62%</t>
+  </si>
+  <si>
+    <t>HDF MELAM 2.5 MM ALB</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>00014929  HDF MELAMINAT ALB 2.5*2800*2070 (MP)</t>
   </si>
   <si>
     <t>20%</t>
   </si>
   <si>
-    <t>00016608  PICIOARE MOBILA (BUC) 67%</t>
-  </si>
-  <si>
-    <t>00004482  PICIOARE CONICE NEGRE (BUC) 63%</t>
-  </si>
-  <si>
-    <t>POL2542</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>00010335  POLIURETAN FASII VR 2542 (KG) 40%</t>
-  </si>
-  <si>
-    <t>00001305  POLIURETAN 2542X2000X2000X20 (B) 36%</t>
-  </si>
-  <si>
-    <t>CANAPEA-MARIA</t>
-  </si>
-  <si>
-    <t>CHERESTEA RAS</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
-    <t>00002310</t>
-  </si>
-  <si>
-    <t>✓ 00002310  CHERESTEA TIVITA RASINOASE (MC)</t>
-  </si>
-  <si>
-    <t>26%</t>
-  </si>
-  <si>
-    <t>✓ 00016024  CHERESTEA TIVITA FAG (MC)</t>
-  </si>
-  <si>
-    <t>00000033  CHERESTEA RASINOASE (MC)</t>
-  </si>
-  <si>
-    <t>00004311  CHERESTEA (MC) 77%</t>
-  </si>
-  <si>
-    <t>00000033  CHERESTEA RASINOASE (MC) 72%</t>
-  </si>
-  <si>
-    <t>CHER FAG</t>
+    <t>înainte: 1.3000</t>
+  </si>
+  <si>
+    <t>00014124  HDF LACUIT HU 2800X2070X2.5 MM ALB (MP)</t>
+  </si>
+  <si>
+    <t>00013002  MDF MELAM.,2 FETE,10MM ALB (MP) 61%</t>
+  </si>
+  <si>
+    <t>00013000  MDF MELAMINAT 2 FETE,25 MM ALB (MP) 56%</t>
+  </si>
+  <si>
+    <t>PAL MELAM ALB</t>
+  </si>
+  <si>
+    <t>00013041  PAL MEL KRONOSPAN 16MM ALB CORP (MP)</t>
+  </si>
+  <si>
+    <t>27%</t>
+  </si>
+  <si>
+    <t>00024875  RESTURI PAL MELAMINAT 18MM (MP)</t>
+  </si>
+  <si>
+    <t>00011922  PAL M ALB (BUC) 77%</t>
+  </si>
+  <si>
+    <t>00000318  PAL ALB (BUC) 67%</t>
+  </si>
+  <si>
+    <t>HSURUB STAS 5/50</t>
+  </si>
+  <si>
+    <t>00008131  SURUB 5X50 (MIIB) 60%</t>
+  </si>
+  <si>
+    <t>00006465  SURUB STAS 7505 5.0X30 (MIIB) 57%</t>
+  </si>
+  <si>
+    <t>HSURUB STAS 5/35</t>
+  </si>
+  <si>
+    <t>00008132  SURUB 5X35 (MIIB) 60%</t>
+  </si>
+  <si>
+    <t>00002852  SURUB STAS 7505 4.0X35 (MIIB) 57%</t>
+  </si>
+  <si>
+    <t>HSURUB 5/25</t>
+  </si>
+  <si>
+    <t>00008132  SURUB 5X35 (MIIB) 56%</t>
+  </si>
+  <si>
+    <t>00017962  SURUB M 4X25 (BUC) 52%</t>
+  </si>
+  <si>
+    <t>HSURUB 4/25</t>
+  </si>
+  <si>
+    <t>00017962  SURUB M 4X25 (BUC) 67%</t>
+  </si>
+  <si>
+    <t>00006436  SURUB LEMN 4X25 (BUC) 60%</t>
+  </si>
+  <si>
+    <t>PICIOARE PLASTIC</t>
+  </si>
+  <si>
+    <t>MIIBUC</t>
+  </si>
+  <si>
+    <t>00012792  PICIORUSE PLASTIC (BUC) 76%</t>
+  </si>
+  <si>
+    <t>00000855  PAHARE PLASTIC (SET) 71%</t>
+  </si>
+  <si>
+    <t>TNT ALB 40</t>
+  </si>
+  <si>
+    <t>00024908  TNT 40 GR MP ALB 1.60 (544MP/ROLA) (MP)</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>00019757  TNT 40 GR/MP ALB H225 (MP) 51%</t>
+  </si>
+  <si>
+    <t>00005957  TNT 35GR/MP ALB (MP) 48%</t>
+  </si>
+  <si>
+    <t>TNT NEGRU 60</t>
+  </si>
+  <si>
+    <t>00024909  TNT 60GR/MP/1,60  NEGRU (360MP/ROLA) (MP)</t>
+  </si>
+  <si>
+    <t>înainte: 4.0000</t>
+  </si>
+  <si>
+    <t>00001096  TNT 50G MP NEGRU 1.60X250 (MP) 59%</t>
+  </si>
+  <si>
+    <t>00007954  TNT 60 GR/MP L=1.60 NEGRU (MP) 56%</t>
+  </si>
+  <si>
+    <t>CHEITE</t>
+  </si>
+  <si>
+    <t>BUC</t>
+  </si>
+  <si>
+    <t>00006183  CHEIE (BUC) 67%</t>
+  </si>
+  <si>
+    <t>00006752  CHEI YALA (BUC) 42%</t>
+  </si>
+  <si>
+    <t>AMESTEC FIBRA</t>
+  </si>
+  <si>
+    <t>00005814</t>
+  </si>
+  <si>
+    <t>✓ 00005814  AMESTEC BURETE+FIBRA (KG)</t>
+  </si>
+  <si>
+    <t>înainte: 2.0000</t>
+  </si>
+  <si>
+    <t>00005919  PERNA CORINA AMESTEC (BUC)</t>
+  </si>
+  <si>
+    <t>00000869  AMESTEC FULGI + FIBRA (KG) 83%</t>
+  </si>
+  <si>
+    <t>00005814  AMESTEC BURETE+FIBRA (KG) 76%</t>
+  </si>
+  <si>
+    <t>FOLIE STRETCH</t>
+  </si>
+  <si>
+    <t>00024988  FOLIE STRETCH MANUALA 1.40 KG (1.40KG FOLIE,130GR. CARTON) (ROLE)</t>
+  </si>
+  <si>
+    <t>00025143  FOLIE STRETCH MANUALA 1.575 KG (1.40 KG FOLIE,175 GR. CARTON (ROLE)</t>
+  </si>
+  <si>
+    <t>00004729  FOLIE STRECH (BUC) 83%</t>
+  </si>
+  <si>
+    <t>00001011  FOLIE STRETCH MANUALA (ROLE) 74%</t>
+  </si>
+  <si>
+    <t>DESEURI DIN CROIRE</t>
+  </si>
+  <si>
+    <t>00017054  DISCURI DEBITARE A60 (BUC) 33%</t>
+  </si>
+  <si>
+    <t>00003671  DISC SLEFUIRE (BUC) 29%</t>
+  </si>
+  <si>
+    <t>BANDA SCOTCH</t>
+  </si>
+  <si>
+    <t>00017581  BANDA (BUC) 57%</t>
+  </si>
+  <si>
+    <t>00007506  BANDA ATC (BUC) 48%</t>
+  </si>
+  <si>
+    <t>CANAPEA-CORINA</t>
+  </si>
+  <si>
+    <t>67%</t>
   </si>
   <si>
     <t>00000034  CHERESTEA FAG (MC)</t>
   </si>
   <si>
-    <t>9%</t>
-  </si>
-  <si>
-    <t>00016024  CHERESTEA TIVITA FAG (MC)</t>
-  </si>
-  <si>
-    <t>00024779  CHERESTEA FAG SS USC (MC)</t>
-  </si>
-  <si>
-    <t>00000034  CHERESTEA FAG (MC) 64%</t>
-  </si>
-  <si>
-    <t>00021033  CHERESTELE FAG (MC) 62%</t>
-  </si>
-  <si>
-    <t>HDF MELAM 2.5 MM ALB</t>
-  </si>
-  <si>
-    <t>MP</t>
-  </si>
-  <si>
-    <t>00014929  HDF MELAMINAT ALB 2.5*2800*2070 (MP)</t>
-  </si>
-  <si>
-    <t>00014124  HDF LACUIT HU 2800X2070X2.5 MM ALB (MP)</t>
+    <t>00002310  CHERESTEA TIVITA RASINOASE (MC)</t>
+  </si>
+  <si>
+    <t>13%</t>
+  </si>
+  <si>
+    <t>00021497  CHERESTEA FAG RINDELUITA (MC)</t>
   </si>
   <si>
     <t>00017947  HDF BRUT 2.5 MM (MP)</t>
   </si>
   <si>
-    <t>00013002  MDF MELAM.,2 FETE,10MM ALB (MP) 61%</t>
-  </si>
-  <si>
-    <t>00013000  MDF MELAMINAT 2 FETE,25 MM ALB (MP) 56%</t>
-  </si>
-  <si>
-    <t>PAL MELAM ALB</t>
-  </si>
-  <si>
-    <t>00013041  PAL MEL KRONOSPAN 16MM ALB CORP (MP)</t>
-  </si>
-  <si>
-    <t>22%</t>
-  </si>
-  <si>
     <t>00019036  PAL MELAMINAT ALB K110 16MM 2800X2070 (MP)</t>
   </si>
   <si>
-    <t>00024875  RESTURI PAL MELAMINAT 18MM (MP)</t>
-  </si>
-  <si>
-    <t>00011922  PAL M ALB (BUC) 77%</t>
-  </si>
-  <si>
-    <t>00000318  PAL ALB (BUC) 67%</t>
-  </si>
-  <si>
-    <t>HSURUB STAS 5/50</t>
-  </si>
-  <si>
-    <t>00022669  SURUB STAS 7505 4.0X60 ZG-500 (MIIB)</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
     <t>00024775  SURUB STAS 7505 4.0X18 ZG (MIIB)</t>
   </si>
   <si>
-    <t>00008131  SURUB 5X50 (MIIB) 60%</t>
-  </si>
-  <si>
-    <t>00006465  SURUB STAS 7505 5.0X30 (MIIB) 57%</t>
-  </si>
-  <si>
-    <t>HSURUB STAS 5/35</t>
-  </si>
-  <si>
-    <t>00008132  SURUB 5X35 (MIIB) 60%</t>
-  </si>
-  <si>
-    <t>00002852  SURUB STAS 7505 4.0X35 (MIIB) 57%</t>
-  </si>
-  <si>
-    <t>HSURUB 5/25</t>
-  </si>
-  <si>
-    <t>00008132  SURUB 5X35 (MIIB) 56%</t>
-  </si>
-  <si>
-    <t>00017962  SURUB M 4X25 (BUC) 52%</t>
-  </si>
-  <si>
-    <t>HSURUB 4/25</t>
-  </si>
-  <si>
-    <t>00017962  SURUB M 4X25 (BUC) 67%</t>
-  </si>
-  <si>
-    <t>00006436  SURUB LEMN 4X25 (BUC) 60%</t>
-  </si>
-  <si>
-    <t>PICIOARE PLASTIC</t>
-  </si>
-  <si>
-    <t>MIIBUC</t>
-  </si>
-  <si>
-    <t>00012792  PICIORUSE PLASTIC (BUC) 76%</t>
-  </si>
-  <si>
-    <t>00000855  PAHARE PLASTIC (SET) 71%</t>
-  </si>
-  <si>
-    <t>TNT ALB 40</t>
-  </si>
-  <si>
-    <t>00023469  TNT 40 GR MP ALB 1.60 (512MP/ROLA) (MP)</t>
-  </si>
-  <si>
-    <t>00024908  TNT 40 GR MP ALB 1.60 (544MP/ROLA) (MP)</t>
-  </si>
-  <si>
-    <t>00019757  TNT 40 GR/MP ALB H225 (MP) 51%</t>
-  </si>
-  <si>
-    <t>00005957  TNT 35GR/MP ALB (MP) 48%</t>
-  </si>
-  <si>
-    <t>TNT NEGRU 60</t>
+    <t>7%</t>
+  </si>
+  <si>
+    <t>HSURUB STAS 5/40</t>
+  </si>
+  <si>
+    <t>00006465  SURUB STAS 7505 5.0X30 (MIIB) 52%</t>
+  </si>
+  <si>
+    <t>00002852  SURUB STAS 7505 4.0X35 (MIIB) 48%</t>
+  </si>
+  <si>
+    <t>HSURUB 8/100</t>
+  </si>
+  <si>
+    <t>00019206  DIBLU SURUB 8X100 (BUC) 67%</t>
+  </si>
+  <si>
+    <t>00002976  SURUB TORBANT 8X100 (MIIB) 57%</t>
+  </si>
+  <si>
+    <t>SAIBE PLATE M8x24x2</t>
+  </si>
+  <si>
+    <t>00006696  SAIBA PLATA SPECIALA M8X24X2 ZA (MIIB)</t>
+  </si>
+  <si>
+    <t>înainte: 0.0120</t>
+  </si>
+  <si>
+    <t>00012799  SAIBE PLATE DIN 9021 M8X24X2 ZA (100B) 70%</t>
+  </si>
+  <si>
+    <t>00010978  SAIBE PLATE DIN 125A-M12X24X2.5 ZA (BUC) 56%</t>
+  </si>
+  <si>
+    <t>HSURUB 5/20</t>
+  </si>
+  <si>
+    <t>00024985  HOLSURUB 2.5X20 (SUTEB) 67%</t>
+  </si>
+  <si>
+    <t>00025075  SURUB LEMN 3.5X20 (BUC) 56%</t>
+  </si>
+  <si>
+    <t>BALAMA PAFTA</t>
+  </si>
+  <si>
+    <t>00010703  BALAMA 40X253 (BUC)</t>
+  </si>
+  <si>
+    <t>00000433  BALAMA (BUC) 73%</t>
+  </si>
+  <si>
+    <t>00001231  BALAMA (B) 73%</t>
+  </si>
+  <si>
+    <t>ROTILA H32</t>
+  </si>
+  <si>
+    <t>00010568</t>
+  </si>
+  <si>
+    <t>✓ 00010568  ROTILA H32 L50 D28 (BUC)</t>
+  </si>
+  <si>
+    <t>53%</t>
+  </si>
+  <si>
+    <t>00010913  ROTILA H35 L45 D30 (  BUC)</t>
+  </si>
+  <si>
+    <t>00010568  ROTILA H32 L50 D28 (BUC) 69%</t>
+  </si>
+  <si>
+    <t>00011950  ROTILA D25 (BUC) 58%</t>
+  </si>
+  <si>
+    <t>CURSORI</t>
+  </si>
+  <si>
+    <t>00000965  CURSORI ALBI (BUC) 78%</t>
+  </si>
+  <si>
+    <t>00003621  CURSOR 3 (BC) 63%</t>
+  </si>
+  <si>
+    <t>OPRITORI PLASTIC</t>
+  </si>
+  <si>
+    <t>00015654  OPRITOR SINA INF PLASTIC (BUC) 68%</t>
+  </si>
+  <si>
+    <t>00001819  MATURI PLASTIC (BUC) 59%</t>
+  </si>
+  <si>
+    <t>00024719  FOLIE STRETCH MANUALA 23 MY (ROLA)</t>
+  </si>
+  <si>
+    <t>00016639  FOLIE STRETCH MANUALA 23 MICR 2,7 KG NET/2.95 KG BRUT (ROLA)</t>
+  </si>
+  <si>
+    <t>CANAPEA-CORINA-II</t>
+  </si>
+  <si>
+    <t>PLACAJ 15</t>
+  </si>
+  <si>
+    <t>00005470  PLACAJ FAG 15 MM (MP) 62%</t>
+  </si>
+  <si>
+    <t>00011332  PLACAJ 2.7 (BUC) 61%</t>
+  </si>
+  <si>
+    <t>KIT CORINA II</t>
+  </si>
+  <si>
+    <t>00014970  KIT CORINA II 2542 (BUC) 80%</t>
+  </si>
+  <si>
+    <t>00014397  SM015 CORINA II (BUC) 63%</t>
+  </si>
+  <si>
+    <t>PLASA BONELL 122x60x9.5</t>
+  </si>
+  <si>
+    <t>00011925  PLASA BONNEL 122*61*9.5 (BUC) 76%</t>
+  </si>
+  <si>
+    <t>00000320  PLASA BONNELL 9.5 (BUC) 73%</t>
+  </si>
+  <si>
+    <t>SAIBE PLATE M8.4x24x1.5</t>
+  </si>
+  <si>
+    <t>00011623  SAIBE PLATE SPECIALE DIN 522C-8,4X24X1.50 (100BU) 59%</t>
+  </si>
+  <si>
+    <t>00012799  SAIBE PLATE DIN 9021 M8X24X2 ZA (100B) 59%</t>
+  </si>
+  <si>
+    <t>ROTILA BILA D40 FLANSA</t>
+  </si>
+  <si>
+    <t>00012815  ROTILA SFERICA PLASTIC D40,FLANSA (BUC) 63%</t>
+  </si>
+  <si>
+    <t>00003770  ROTILA CU FLANSA 40MM (BUC) 58%</t>
+  </si>
+  <si>
+    <t>ROTILA 30 MM SW12 NEGRU</t>
+  </si>
+  <si>
+    <t>00013313  ROTILA 32 MM SW12 NEGRU (BUC) 88%</t>
+  </si>
+  <si>
+    <t>00019357  ROTILA 32 MM FIXA NEGRU (BUC) 64%</t>
+  </si>
+  <si>
+    <t>CAPSE 380/12</t>
+  </si>
+  <si>
+    <t>00009232  CAPSE 80/12 (CUT) 81%</t>
+  </si>
+  <si>
+    <t>00000022  CAPSE 380/10 (BUC) 79%</t>
+  </si>
+  <si>
+    <t>TNT NEGRU</t>
+  </si>
+  <si>
+    <t>00019202  CANT NEGRU (M) 70%</t>
+  </si>
+  <si>
+    <t>00014549  TNT 50 GR/MP NEGRU (MP) 65%</t>
+  </si>
+  <si>
+    <t>CL-ECO</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>00024369  CHERESTEA TIVITA PIN (MC)</t>
+  </si>
+  <si>
+    <t>00002838  CHERESTEA TIVITA RASINOASE USCATA (MC)</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>00016186  MDF 2.5 MM 2800X2070 (MP)</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>POL ECO SM011</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>00012186  SM011 ECO (BUC) 62%</t>
+  </si>
+  <si>
+    <t>00008694  ECO STICK (BUC) 31%</t>
   </si>
   <si>
     <t>00020637  TNT 60GR/MP/1,60  NEGRU (400 MP/ROLA) (MP)</t>
   </si>
   <si>
-    <t>00024909  TNT 60GR/MP/1,60  NEGRU (360MP/ROLA) (MP)</t>
-  </si>
-  <si>
-    <t>00001096  TNT 50G MP NEGRU 1.60X250 (MP) 59%</t>
-  </si>
-  <si>
-    <t>00007954  TNT 60 GR/MP L=1.60 NEGRU (MP) 56%</t>
-  </si>
-  <si>
-    <t>CHEITE</t>
-  </si>
-  <si>
-    <t>BUC</t>
-  </si>
-  <si>
-    <t>00006183  CHEIE (BUC) 67%</t>
-  </si>
-  <si>
-    <t>00006752  CHEI YALA (BUC) 42%</t>
-  </si>
-  <si>
-    <t>AMESTEC FIBRA</t>
-  </si>
-  <si>
-    <t>00005814</t>
-  </si>
-  <si>
-    <t>✓ 00005814  AMESTEC BURETE+FIBRA (KG)</t>
-  </si>
-  <si>
-    <t>61%</t>
-  </si>
-  <si>
-    <t>00005919  PERNA CORINA AMESTEC (BUC)</t>
-  </si>
-  <si>
-    <t>00000869  AMESTEC FULGI + FIBRA (KG) 83%</t>
-  </si>
-  <si>
-    <t>00005814  AMESTEC BURETE+FIBRA (KG) 76%</t>
-  </si>
-  <si>
-    <t>FOLIE STRETCH</t>
-  </si>
-  <si>
-    <t>00024719  FOLIE STRETCH MANUALA 23 MY (ROLA)</t>
-  </si>
-  <si>
-    <t>00024817  FOLIE STRETCH MANUALA 23 MICR 2.75 KG (ROLA)</t>
-  </si>
-  <si>
-    <t>00024988  FOLIE STRETCH MANUALA 1.40 KG (1.40KG FOLIE,130GR. CARTON) (ROLE)</t>
-  </si>
-  <si>
-    <t>00004729  FOLIE STRECH (BUC) 83%</t>
-  </si>
-  <si>
-    <t>00001011  FOLIE STRETCH MANUALA (ROLE) 74%</t>
-  </si>
-  <si>
-    <t>DESEURI DIN CROIRE</t>
-  </si>
-  <si>
-    <t>00017054  DISCURI DEBITARE A60 (BUC) 33%</t>
-  </si>
-  <si>
-    <t>00003671  DISC SLEFUIRE (BUC) 29%</t>
-  </si>
-  <si>
-    <t>BANDA SCOTCH</t>
-  </si>
-  <si>
-    <t>00017581  BANDA (BUC) 57%</t>
-  </si>
-  <si>
-    <t>00007506  BANDA ATC (BUC) 48%</t>
-  </si>
-  <si>
-    <t>CANAPEA-CORINA</t>
-  </si>
-  <si>
-    <t>00016024</t>
-  </si>
-  <si>
-    <t>59%</t>
-  </si>
-  <si>
-    <t>00002310  CHERESTEA TIVITA RASINOASE (MC)</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>00024626  CHERESTEA FAG CLS B (MC)</t>
-  </si>
-  <si>
-    <t>29%</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>00020017  SURUB STAS 7505 4.0X50 ZG IMPORT-1000/4.000 (MIIB)</t>
-  </si>
-  <si>
-    <t>HSURUB STAS 5/40</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>00006465  SURUB STAS 7505 5.0X30 (MIIB) 52%</t>
-  </si>
-  <si>
-    <t>00002852  SURUB STAS 7505 4.0X35 (MIIB) 48%</t>
-  </si>
-  <si>
-    <t>HSURUB 8/100</t>
-  </si>
-  <si>
-    <t>00019206  DIBLU SURUB 8X100 (BUC) 67%</t>
-  </si>
-  <si>
-    <t>00002976  SURUB TORBANT 8X100 (MIIB) 57%</t>
-  </si>
-  <si>
-    <t>SAIBE PLATE M8x24x2</t>
-  </si>
-  <si>
-    <t>00006696  SAIBA PLATA SPECIALA M8X24X2 ZA (MIIB)</t>
-  </si>
-  <si>
-    <t>00012799  SAIBE PLATE DIN 9021 M8X24X2 ZA (100B) 70%</t>
-  </si>
-  <si>
-    <t>00010978  SAIBE PLATE DIN 125A-M12X24X2.5 ZA (BUC) 56%</t>
-  </si>
-  <si>
-    <t>HSURUB 5/20</t>
-  </si>
-  <si>
-    <t>00024985  HOLSURUB 2.5X20 (SUTEB) 67%</t>
-  </si>
-  <si>
-    <t>00025075  SURUB LEMN 3.5X20 (BUC) 56%</t>
-  </si>
-  <si>
-    <t>BALAMA PAFTA</t>
-  </si>
-  <si>
-    <t>00010703  BALAMA 40X253 (BUC)</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>00000433  BALAMA (BUC) 73%</t>
-  </si>
-  <si>
-    <t>00001231  BALAMA (B) 73%</t>
-  </si>
-  <si>
-    <t>ROTILA H32</t>
-  </si>
-  <si>
-    <t>00010568</t>
-  </si>
-  <si>
-    <t>✓ 00010568  ROTILA H32 L50 D28 (BUC)</t>
-  </si>
-  <si>
-    <t>00010913  ROTILA H35 L45 D30 (  BUC)</t>
-  </si>
-  <si>
-    <t>00010568  ROTILA H32 L50 D28 (BUC) 69%</t>
-  </si>
-  <si>
-    <t>00011950  ROTILA D25 (BUC) 58%</t>
-  </si>
-  <si>
-    <t>CURSORI</t>
-  </si>
-  <si>
-    <t>00000965  CURSORI ALBI (BUC) 78%</t>
-  </si>
-  <si>
-    <t>00003621  CURSOR 3 (BC) 63%</t>
-  </si>
-  <si>
-    <t>OPRITORI PLASTIC</t>
-  </si>
-  <si>
-    <t>00015654  OPRITOR SINA INF PLASTIC (BUC) 68%</t>
-  </si>
-  <si>
-    <t>00001819  MATURI PLASTIC (BUC) 59%</t>
-  </si>
-  <si>
-    <t>00016639  FOLIE STRETCH MANUALA 23 MICR 2,7 KG NET/2.95 KG BRUT (ROLA)</t>
-  </si>
-  <si>
-    <t>CANAPEA-CORINA-II</t>
-  </si>
-  <si>
-    <t>PLACAJ 15</t>
-  </si>
-  <si>
-    <t>00005470  PLACAJ FAG 15 MM (MP) 62%</t>
-  </si>
-  <si>
-    <t>00011332  PLACAJ 2.7 (BUC) 61%</t>
-  </si>
-  <si>
-    <t>KIT CORINA II</t>
-  </si>
-  <si>
-    <t>00014970  KIT CORINA II 2542 (BUC) 80%</t>
-  </si>
-  <si>
-    <t>00014397  SM015 CORINA II (BUC) 63%</t>
-  </si>
-  <si>
-    <t>PLASA BONELL 122x60x9.5</t>
-  </si>
-  <si>
-    <t>00011925  PLASA BONNEL 122*61*9.5 (BUC) 76%</t>
-  </si>
-  <si>
-    <t>00000320  PLASA BONNELL 9.5 (BUC) 73%</t>
-  </si>
-  <si>
-    <t>SAIBE PLATE M8.4x24x1.5</t>
-  </si>
-  <si>
-    <t>00011623  SAIBE PLATE SPECIALE DIN 522C-8,4X24X1.50 (100BU) 59%</t>
-  </si>
-  <si>
-    <t>00012799  SAIBE PLATE DIN 9021 M8X24X2 ZA (100B) 59%</t>
-  </si>
-  <si>
-    <t>ROTILA BILA D40 FLANSA</t>
-  </si>
-  <si>
-    <t>00012815  ROTILA SFERICA PLASTIC D40,FLANSA (BUC) 63%</t>
-  </si>
-  <si>
-    <t>00003770  ROTILA CU FLANSA 40MM (BUC) 58%</t>
-  </si>
-  <si>
-    <t>ROTILA 30 MM SW12 NEGRU</t>
-  </si>
-  <si>
-    <t>00013313  ROTILA 32 MM SW12 NEGRU (BUC) 88%</t>
-  </si>
-  <si>
-    <t>00019357  ROTILA 32 MM FIXA NEGRU (BUC) 64%</t>
-  </si>
-  <si>
-    <t>CAPSE 380/12</t>
-  </si>
-  <si>
-    <t>00009232  CAPSE 80/12 (CUT) 81%</t>
-  </si>
-  <si>
-    <t>00000022  CAPSE 380/10 (BUC) 79%</t>
-  </si>
-  <si>
-    <t>TNT NEGRU</t>
-  </si>
-  <si>
-    <t>00019202  CANT NEGRU (M) 70%</t>
-  </si>
-  <si>
-    <t>00014549  TNT 50 GR/MP NEGRU (MP) 65%</t>
-  </si>
-  <si>
-    <t>CL-ECO</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>00024369  CHERESTEA TIVITA PIN (MC)</t>
-  </si>
-  <si>
-    <t>00002838  CHERESTEA TIVITA RASINOASE USCATA (MC)</t>
-  </si>
-  <si>
-    <t>00021497  CHERESTEA FAG RINDELUITA (MC)</t>
-  </si>
-  <si>
-    <t>POL ECO SM011</t>
-  </si>
-  <si>
-    <t>SET</t>
-  </si>
-  <si>
-    <t>00012186  SM011 ECO (BUC) 62%</t>
-  </si>
-  <si>
-    <t>00008694  ECO STICK (BUC) 31%</t>
+    <t>00010744  CURSOR 5 (BUC)</t>
   </si>
   <si>
     <t>HOLZSURUB 5X40</t>
@@ -610,6 +619,9 @@
     <t>SURUB TORBANT 6X35</t>
   </si>
   <si>
+    <t>00019798  SURUB TORBANT DIN 603 6X30 ZA (MIIB)</t>
+  </si>
+  <si>
     <t>00002987  SURUB TORBANT (BUC) 80%</t>
   </si>
   <si>
@@ -644,6 +656,9 @@
   </si>
   <si>
     <t>ROLA</t>
+  </si>
+  <si>
+    <t>00018725  FOLIE PE 1800X0.06 (KG)</t>
   </si>
   <si>
     <t>FOLIE TUB SACI</t>
@@ -1042,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1057,7 +1072,7 @@
     <col min="10" max="13" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1097,37 +1112,40 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2">
         <v>0.3</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2">
         <v>0.0526</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
         <v>20</v>
@@ -1138,901 +1156,967 @@
       <c r="M2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2">
         <v>0.004</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="2">
         <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2">
         <v>0.24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="M4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2">
         <v>0.0255</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I5" s="2">
         <v>0.025</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2">
         <v>0.0234</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="M6" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2">
         <v>1.133</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I7" s="2">
         <v>1.5</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="1">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L8" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="M8" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2">
         <v>0.08</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
         <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0.012</v>
-      </c>
-      <c r="J9" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" t="s">
-        <v>68</v>
-      </c>
-      <c r="M9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="1">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
       </c>
       <c r="E10" s="2">
         <v>0.08</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0.024</v>
+        <v>17</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="N10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2">
         <v>0.02</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L11" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="M11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="N11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2">
         <v>0.14</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="M12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="N12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1">
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2">
         <v>0.004</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="M13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="N13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2">
         <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" t="s">
         <v>84</v>
       </c>
-      <c r="H14" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" s="2">
-        <v>5</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="N14" t="s">
         <v>85</v>
       </c>
-      <c r="K14" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" t="s">
-        <v>86</v>
-      </c>
-      <c r="M14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2">
         <v>2</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I15" s="2">
         <v>2</v>
       </c>
       <c r="J15" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15" t="s">
+        <v>89</v>
+      </c>
+      <c r="N15" t="s">
         <v>90</v>
       </c>
-      <c r="K15" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" t="s">
-        <v>91</v>
-      </c>
-      <c r="M15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E16" s="2">
         <v>4</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L16" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="M16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="N16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2">
         <v>3</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="I17" s="2">
         <v>3</v>
       </c>
       <c r="J17" t="s">
+        <v>98</v>
+      </c>
+      <c r="K17" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" t="s">
+        <v>100</v>
+      </c>
+      <c r="N17" t="s">
         <v>101</v>
       </c>
-      <c r="K17" t="s">
-        <v>16</v>
-      </c>
-      <c r="L17" t="s">
-        <v>102</v>
-      </c>
-      <c r="M17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E18" s="2">
         <v>0.13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" t="s">
+        <v>104</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" t="s">
         <v>105</v>
       </c>
-      <c r="H18" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="N18" t="s">
         <v>106</v>
       </c>
-      <c r="K18" t="s">
-        <v>107</v>
-      </c>
-      <c r="L18" t="s">
-        <v>108</v>
-      </c>
-      <c r="M18" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L19" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="N19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="1">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E20" s="2">
         <v>0.2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L20" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="M20" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="N20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B21" s="1">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2">
         <v>0.0237</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>117</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I21" s="2">
         <v>0.023</v>
       </c>
       <c r="J21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" t="s">
+        <v>115</v>
+      </c>
+      <c r="L21" t="s">
+        <v>116</v>
+      </c>
+      <c r="M21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" t="s">
         <v>44</v>
       </c>
-      <c r="K21" t="s">
-        <v>119</v>
-      </c>
-      <c r="L21" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B22" s="1">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2">
         <v>0.02</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="H22" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I22" s="2">
         <v>0.03</v>
       </c>
       <c r="J22" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="L22" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="M22" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B23" s="1">
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2">
         <v>1.33</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H23" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="I23" s="2">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="K23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L23" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="M23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="N23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B24" s="1">
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2">
         <v>1.2</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H24" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="I24" s="2">
         <v>1.2</v>
       </c>
       <c r="J24" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="L24" t="s">
         <v>62</v>
@@ -2040,2383 +2124,2560 @@
       <c r="M24" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B25" s="1">
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" s="2">
         <v>0.08</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I25" s="2">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="J25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M25" t="s">
+        <v>66</v>
+      </c>
+      <c r="N25" t="s">
         <v>67</v>
       </c>
-      <c r="K25" t="s">
-        <v>16</v>
-      </c>
-      <c r="L25" t="s">
-        <v>68</v>
-      </c>
-      <c r="M25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B26" s="1">
         <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" s="2">
         <v>0.08</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="H26" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I26" s="2">
         <v>0.024</v>
       </c>
       <c r="J26" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M26" t="s">
         <v>124</v>
       </c>
-      <c r="K26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L26" t="s">
-        <v>127</v>
-      </c>
-      <c r="M26" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B27" s="1">
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" s="2">
         <v>0.04</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L27" t="s">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="M27" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="N27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B28" s="1">
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E28" s="2">
         <v>0.04</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H28" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I28" s="2">
         <v>0.024</v>
       </c>
       <c r="J28" t="s">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="K28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L28" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="M28" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="N28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B29" s="1">
         <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E29" s="2">
         <v>0.02</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L29" t="s">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="M29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="N29" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B30" s="1">
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E30" s="2">
         <v>0.14</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L30" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="M30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="N30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B31" s="1">
         <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2">
         <v>2</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H31" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="I31" s="2">
         <v>2</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L31" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="M31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="N31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B32" s="1">
         <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E32" s="2">
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G32" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H32" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="I32" s="2">
         <v>4</v>
       </c>
       <c r="J32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" t="s">
+        <v>145</v>
+      </c>
+      <c r="L32" t="s">
+        <v>17</v>
+      </c>
+      <c r="M32" t="s">
+        <v>146</v>
+      </c>
+      <c r="N32" t="s">
         <v>147</v>
       </c>
-      <c r="K32" t="s">
-        <v>16</v>
-      </c>
-      <c r="L32" t="s">
-        <v>148</v>
-      </c>
-      <c r="M32" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B33" s="1">
         <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E33" s="2">
         <v>0.004</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L33" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="M33" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="N33" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B34" s="1">
         <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E34" s="2">
         <v>3</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L34" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="M34" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="N34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B35" s="1">
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E35" s="2">
         <v>2</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="M35" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="N35" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B36" s="1">
         <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E36" s="2">
         <v>0.13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="H36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I36" s="2">
         <v>0.3</v>
       </c>
       <c r="J36" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="L36" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="M36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="N36" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B37" s="1">
         <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E37" s="2">
         <v>2</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L37" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="M37" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="N37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B38" s="1">
         <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E38" s="2">
         <v>0.2</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L38" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="M38" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="N38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B39" s="1">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E39" s="2">
         <v>0.027</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L39" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="M39" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="N39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B40" s="1">
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E40" s="2">
         <v>0.02</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L40" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="M40" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B41" s="1">
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E41" s="2">
         <v>0.9</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L41" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="M41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="N41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="1">
         <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E42" s="2">
         <v>0.654</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L42" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="M42" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B43" s="1">
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E43" s="2">
         <v>0.2</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L43" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" t="s">
+        <v>158</v>
+      </c>
+      <c r="N43" t="s">
         <v>159</v>
       </c>
-      <c r="M43" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="1">
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E44" s="2">
         <v>1</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L44" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" t="s">
+        <v>161</v>
+      </c>
+      <c r="N44" t="s">
         <v>162</v>
       </c>
-      <c r="M44" t="s">
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="1">
+        <v>17</v>
+      </c>
+      <c r="C45" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>157</v>
-      </c>
-      <c r="B45" s="1">
-        <v>17</v>
-      </c>
-      <c r="C45" t="s">
-        <v>164</v>
-      </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E45" s="2">
         <v>2</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M45" t="s">
+        <v>164</v>
+      </c>
+      <c r="N45" t="s">
         <v>165</v>
       </c>
-      <c r="M45" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B46" s="1">
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E46" s="2">
         <v>0.22</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L46" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M46" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="N46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B47" s="1">
         <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E47" s="2">
         <v>0.08</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L47" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="M47" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="N47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B48" s="1">
         <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E48" s="2">
         <v>0.08</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L48" t="s">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="N48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B49" s="1">
         <v>23</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49" s="2">
         <v>0.08</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L49" t="s">
+        <v>17</v>
+      </c>
+      <c r="M49" t="s">
+        <v>167</v>
+      </c>
+      <c r="N49" t="s">
         <v>168</v>
       </c>
-      <c r="M49" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B50" s="1">
         <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E50" s="2">
         <v>0.2</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L50" t="s">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="M50" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="N50" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B51" s="1">
         <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E51" s="2">
         <v>0.2</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L51" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="M51" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="N51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="1">
         <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D52" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E52" s="2">
         <v>2</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L52" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" t="s">
+        <v>170</v>
+      </c>
+      <c r="N52" t="s">
         <v>171</v>
       </c>
-      <c r="M52" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B53" s="1">
         <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E53" s="2">
         <v>2</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L53" t="s">
+        <v>17</v>
+      </c>
+      <c r="M53" t="s">
+        <v>173</v>
+      </c>
+      <c r="N53" t="s">
         <v>174</v>
       </c>
-      <c r="M53" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B54" s="1">
         <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E54" s="2">
         <v>1</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L54" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" t="s">
+        <v>176</v>
+      </c>
+      <c r="N54" t="s">
         <v>177</v>
       </c>
-      <c r="M54" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B55" s="1">
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D55" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E55" s="2">
         <v>0.004</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L55" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="M55" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="N55" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B56" s="1">
         <v>39</v>
       </c>
       <c r="C56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E56" s="2">
         <v>4.5</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L56" t="s">
+        <v>17</v>
+      </c>
+      <c r="M56" t="s">
+        <v>179</v>
+      </c>
+      <c r="N56" t="s">
         <v>180</v>
       </c>
-      <c r="M56" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B57" s="1">
         <v>41</v>
       </c>
       <c r="C57" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D57" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E57" s="2">
         <v>2</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L57" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="M57" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="N57" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B58" s="1">
         <v>46</v>
       </c>
       <c r="C58" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E58" s="2">
         <v>2</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L58" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="M58" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="N58" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B59" s="1">
         <v>47</v>
       </c>
       <c r="C59" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D59" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E59" s="2">
         <v>0.3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L59" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="M59" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="N59" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B60" s="1">
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E60" s="2">
         <v>0.0292</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H60" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I60" s="2">
         <v>0.04</v>
       </c>
       <c r="J60" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" t="s">
+        <v>183</v>
+      </c>
+      <c r="L60" t="s">
         <v>184</v>
       </c>
-      <c r="K60" t="s">
-        <v>185</v>
-      </c>
-      <c r="L60" t="s">
-        <v>41</v>
-      </c>
       <c r="M60" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="N60" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B61" s="1">
         <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E61" s="2">
         <v>0.0347</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I61" s="2">
         <v>0.04</v>
       </c>
       <c r="J61" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="L61" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="M61" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N61" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B62" s="1">
         <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E62" s="2">
         <v>2.44</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H62" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I62" s="2">
         <v>3</v>
       </c>
       <c r="J62" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="K62" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="L62" t="s">
-        <v>55</v>
+        <v>186</v>
       </c>
       <c r="M62" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="N62" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B63" s="1">
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E63" s="2">
         <v>2.23</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H63" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I63" s="2">
         <v>3</v>
       </c>
       <c r="J63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L63" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="M63" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N63" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B64" s="1">
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D64" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E64" s="2">
         <v>1</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L64" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="M64" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N64" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B65" s="1">
         <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D65" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E65" s="2">
         <v>2</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G65" t="s">
+        <v>138</v>
+      </c>
+      <c r="H65" t="s">
+        <v>185</v>
+      </c>
+      <c r="I65" s="2">
+        <v>2</v>
+      </c>
+      <c r="J65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65" t="s">
+        <v>17</v>
+      </c>
+      <c r="L65" t="s">
+        <v>17</v>
+      </c>
+      <c r="M65" t="s">
+        <v>139</v>
+      </c>
+      <c r="N65" t="s">
         <v>140</v>
       </c>
-      <c r="H65" t="s">
-        <v>183</v>
-      </c>
-      <c r="I65" s="2">
-        <v>4</v>
-      </c>
-      <c r="J65" t="s">
-        <v>16</v>
-      </c>
-      <c r="K65" t="s">
-        <v>16</v>
-      </c>
-      <c r="L65" t="s">
-        <v>142</v>
-      </c>
-      <c r="M65" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B66" s="1">
         <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E66" s="2">
         <v>10</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="H66" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>16</v>
+        <v>182</v>
+      </c>
+      <c r="I66" s="2">
+        <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L66" t="s">
+        <v>17</v>
+      </c>
+      <c r="M66" t="s">
+        <v>179</v>
+      </c>
+      <c r="N66" t="s">
         <v>180</v>
       </c>
-      <c r="M66" t="s">
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>182</v>
       </c>
       <c r="B67" s="1">
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E67" s="2">
         <v>6</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c r="H67" t="s">
-        <v>16</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>16</v>
+        <v>182</v>
+      </c>
+      <c r="I67" s="2">
+        <v>12</v>
       </c>
       <c r="J67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L67" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="M67" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="N67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B68" s="1">
         <v>29</v>
       </c>
       <c r="C68" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E68" s="2">
         <v>0.14</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L68" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="M68" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="N68" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B69" s="1">
         <v>30</v>
       </c>
       <c r="C69" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E69" s="2">
         <v>0.13</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L69" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="M69" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="N69" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B70" s="1">
         <v>31</v>
       </c>
       <c r="C70" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E70" s="2">
         <v>0.14</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L70" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="M70" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="N70" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B71" s="1">
         <v>32</v>
       </c>
       <c r="C71" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E71" s="2">
         <v>0.04</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L71" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="M71" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="N71" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B72" s="1">
         <v>33</v>
       </c>
       <c r="C72" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E72" s="2">
         <v>0.06</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L72" t="s">
-        <v>192</v>
+        <v>17</v>
       </c>
       <c r="M72" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="N72" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B73" s="1">
         <v>36</v>
       </c>
       <c r="C73" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E73" s="2">
         <v>0.04</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G73" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="H73" t="s">
-        <v>16</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>16</v>
+        <v>182</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0.012</v>
       </c>
       <c r="J73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L73" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="M73" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="N73" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B74" s="1">
         <v>37</v>
       </c>
       <c r="C74" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E74" s="2">
         <v>0.04</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="H74" t="s">
-        <v>16</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>16</v>
+        <v>182</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0.012</v>
       </c>
       <c r="J74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L74" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="M74" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="N74" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B75" s="1">
         <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D75" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E75" s="2">
         <v>4</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G75" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H75" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I75" s="2">
         <v>4</v>
       </c>
       <c r="J75" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75" t="s">
+        <v>145</v>
+      </c>
+      <c r="L75" t="s">
+        <v>17</v>
+      </c>
+      <c r="M75" t="s">
+        <v>146</v>
+      </c>
+      <c r="N75" t="s">
         <v>147</v>
       </c>
-      <c r="K75" t="s">
-        <v>16</v>
-      </c>
-      <c r="L75" t="s">
-        <v>148</v>
-      </c>
-      <c r="M75" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B76" s="1">
         <v>40</v>
       </c>
       <c r="C76" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D76" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E76" s="2">
         <v>2</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L76" t="s">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="M76" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="N76" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B77" s="1">
         <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E77" s="2">
         <v>2</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G77" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H77" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I77" s="2">
         <v>2</v>
       </c>
       <c r="J77" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="K77" t="s">
-        <v>16</v>
+        <v>209</v>
       </c>
       <c r="L77" t="s">
+        <v>21</v>
+      </c>
+      <c r="M77" t="s">
+        <v>176</v>
+      </c>
+      <c r="N77" t="s">
         <v>177</v>
       </c>
-      <c r="M77" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B78" s="1">
         <v>46</v>
       </c>
       <c r="C78" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E78" s="2">
         <v>0.013</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G78" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H78" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I78" s="2">
         <v>0.014</v>
       </c>
       <c r="J78" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K78" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L78" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="N78" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B79" s="1">
         <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D79" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E79" s="2">
         <v>0.4</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G79" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="H79" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I79" s="2">
         <v>0.3</v>
       </c>
       <c r="J79" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K79" t="s">
-        <v>16</v>
+        <v>155</v>
       </c>
       <c r="L79" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="M79" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="N79" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B80" s="1">
         <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D80" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E80" s="2">
         <v>2</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L80" t="s">
-        <v>212</v>
+        <v>17</v>
       </c>
       <c r="M80" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="N80" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B81" s="1">
         <v>51</v>
       </c>
       <c r="C81" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D81" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E81" s="2">
         <v>0.5</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L81" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="M81" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="N81" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B82" s="1">
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D82" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E82" s="2">
         <v>3</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L82" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="M82" t="s">
-        <v>112</v>
+        <v>108</v>
+      </c>
+      <c r="N82" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
